--- a/output/pdf_financials_xlsx/NWST.xlsx
+++ b/output/pdf_financials_xlsx/NWST.xlsx
@@ -5923,52 +5923,52 @@
         <v>2.812699</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.454503</v>
+        <v>6.492636</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.704568</v>
+        <v>6.812545</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.162333</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.267681</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.478017</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.485416</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.543288</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.221959</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.175345</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.007771999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.821084000000001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>19.399425</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>21.767921</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>21.835912</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>21.835912</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>21.1205</v>
       </c>
     </row>
     <row r="93">
@@ -10292,7 +10292,11 @@
           <t>Share-based payment reserve 7 21,488,518</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -12238,7 +12242,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -13865,7 +13873,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15465,7 +15477,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -17493,7 +17509,11 @@
           <t>Share-based payment reserve 11 19,399,425</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -19279,7 +19299,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -19378,7 +19402,11 @@
           <t>Share-based payment reserve 14</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -20776,7 +20804,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -20877,7 +20909,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -21455,7 +21491,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -22720,7 +22760,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -23326,7 +23370,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -23827,7 +23875,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NWST.xlsx
+++ b/output/pdf_financials_xlsx/NWST.xlsx
@@ -1057,52 +1057,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.383905</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.061172</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.021623</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.072463</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.023575</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.022649</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004254</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001915</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.006855</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00713</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011171</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.013861</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.093821</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.022558</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.011858</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2029,52 +2029,52 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.985436</v>
+        <v>-2.369341</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.710915</v>
+        <v>-1.772087</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.743931</v>
+        <v>-1.765554</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.765558</v>
+        <v>-1.838021</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.937118</v>
+        <v>-2.960693</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.827666</v>
+        <v>-1.850315</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.544725</v>
+        <v>-0.548979</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.427269</v>
+        <v>-0.427852</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.894424</v>
+        <v>-0.896339</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.185601</v>
+        <v>-3.192456</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.171749</v>
+        <v>0.164619</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.505444</v>
+        <v>-3.516615</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.505444</v>
+        <v>-3.519305</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-21.429908</v>
+        <v>-21.523729</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-7.383905</v>
+        <v>-7.406463</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.691281</v>
+        <v>-3.703139</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2149,52 +2149,52 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.985436</v>
+        <v>-2.369341</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.710915</v>
+        <v>-1.772087</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.743511</v>
+        <v>-1.765134</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.754763</v>
+        <v>-1.827226</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.922645</v>
+        <v>-2.94622</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.815908</v>
+        <v>-1.838557</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.539181</v>
+        <v>-0.543435</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.42536</v>
+        <v>-0.425943</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.893087</v>
+        <v>-0.895002</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.184665</v>
+        <v>-3.19152</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.172404</v>
+        <v>0.165274</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.479898</v>
+        <v>-3.491069</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.45249</v>
+        <v>-3.466351</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-21.301251</v>
+        <v>-21.395072</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-7.284422</v>
+        <v>-7.30698</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.68137</v>
+        <v>-3.693228</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2496,19 +2496,19 @@
         <v>1.802817</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.5118470000000001</v>
+        <v>24.682958</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.378353</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.231037</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.231037</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.280174</v>
       </c>
     </row>
     <row r="35">
@@ -2612,19 +2612,19 @@
         <v>1.802817</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.541847</v>
+        <v>24.712958</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.408353</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.261037</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.261037</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.310174</v>
       </c>
     </row>
     <row r="37">
@@ -3308,19 +3308,19 @@
         <v>0.017743</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>24.384338</v>
+        <v>0.213227</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.747505</v>
+        <v>0.369152</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.629078</v>
+        <v>1.398041</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.629078</v>
+        <v>1.398041</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.434963</v>
+        <v>0.154789</v>
       </c>
     </row>
     <row r="49">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -18392,7 +18392,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -19895,7 +19899,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -21693,7 +21701,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -22378,7 +22390,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -23065,7 +23081,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -28465,7 +28485,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -29607,7 +29631,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -45914,7 +45942,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -73211,7 +73243,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -73508,7 +73540,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -77490,7 +77522,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -85809,7 +85841,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -92092,7 +92124,7 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E839" s="5" t="n">

--- a/output/pdf_financials_xlsx/NWST.xlsx
+++ b/output/pdf_financials_xlsx/NWST.xlsx
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.305096</v>
+        <v>0.370071</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.239916</v>
+        <v>0.304916</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.5019</v>
+        <v>0.5789</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.444678</v>
+        <v>0.5239279999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.464253</v>
+        <v>0.534253</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.325806</v>
+        <v>0.364223</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.309187</v>
+        <v>0.327937</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.199898</v>
@@ -780,25 +780,25 @@
         <v>0.314536</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.363265</v>
+        <v>0.375765</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.332508</v>
+        <v>0.383508</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.469161</v>
+        <v>0.548542</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.528289</v>
+        <v>0.604289</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.187993</v>
+        <v>2.855862</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.03813</v>
+        <v>2.565773</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.633686</v>
+        <v>1.458253</v>
       </c>
       <c r="R7" s="1" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.42689</v>
+        <v>0.491865</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.241336</v>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.701892</v>
+        <v>-0.701892</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.990137</v>
+        <v>-0.990137</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.237</v>
+        <v>-0.237</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016799</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7208,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.065162</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016799</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
         <v>-0.714977</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.197198</v>
+        <v>-1.213997</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.387435</v>
@@ -36632,7 +36632,11 @@
           <t>Proceeds from share issuances 11 33,006,000</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -40760,7 +40764,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -47162,7 +47170,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -47671,7 +47683,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E394" s="5" t="n">
         <v>-0.701892</v>
       </c>
@@ -48673,7 +48689,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -48774,7 +48794,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -50588,7 +50612,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -59058,7 +59086,11 @@
           <t>Salaries and director fees 10</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
@@ -72544,7 +72576,11 @@
           <t>Director fees 15</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -76839,7 +76875,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E686" t="inlineStr">
         <is>
           <t>-</t>
@@ -80742,7 +80782,11 @@
           <t>Director fees 11</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
           <t>-</t>
@@ -88031,7 +88075,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D798" t="inlineStr"/>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E798" s="5" t="n">
         <v>0.064975</v>
       </c>
@@ -92524,7 +92572,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E843" t="inlineStr">
         <is>
           <t>-</t>
@@ -94435,7 +94487,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E862" t="inlineStr">
         <is>
           <t>-</t>
@@ -96033,7 +96089,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E878" s="5" t="n">
         <v>0.701892</v>
       </c>
